--- a/TIMES-NZ/v303/SuppXLS/Demands/Dem_Alloc+Series.xlsx
+++ b/TIMES-NZ/v303/SuppXLS/Demands/Dem_Alloc+Series.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E399"/>
+  <dimension ref="A1:E464"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -478,7 +478,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ADCF-IRG</t>
+          <t>ADCF-Bike-MoTP-Mob</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -505,7 +505,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ADCF-LT</t>
+          <t>ADCF-HRECSys-RFGR</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -532,7 +532,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ADCF-MoTP-Mob</t>
+          <t>ADCF-Hreco-WH</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -559,7 +559,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ADCF-MoTP-Stat</t>
+          <t>ADCF-IRG</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -586,7 +586,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ADCF-PUMP</t>
+          <t>ADCF-LT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ADCF-RFGR</t>
+          <t>ADCF-MTr-MoTP-Mob</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ADCF-WH</t>
+          <t>ADCF-MoTP-Stat</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -667,12 +667,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AFISH-LT</t>
+          <t>ADCF-PUMP</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AGR_AFISH_DMD</t>
+          <t>AGR_ADCF_DMD</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -694,12 +694,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>AFISH-MoTP-Mob</t>
+          <t>ADCF-RF-RFGR</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AGR_AFISH_DMD</t>
+          <t>AGR_ADCF_DMD</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -721,12 +721,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>AFISH-MoTP-Stat</t>
+          <t>ADCF-Trac-MoTP-Mob</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AGR_AFISH_DMD</t>
+          <t>AGR_ADCF_DMD</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>AFISH-OTH</t>
+          <t>ADCF-Uti-MoTP-Mob</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>AGR_AFISH_DMD</t>
+          <t>AGR_ADCF_DMD</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -775,12 +775,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>AFISH-RFGR</t>
+          <t>ADCF-WH</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>AGR_AFISH_DMD</t>
+          <t>AGR_ADCF_DMD</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>AFORE-LT</t>
+          <t>AFISH-Boat-MoTP-Mob</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AGR_AFORE_DMD</t>
+          <t>AGR_AFISH_DMD</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -829,12 +829,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>AFORE-MoTP-Mob</t>
+          <t>AFISH-LT</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>AGR_AFORE_DMD</t>
+          <t>AGR_AFISH_DMD</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -856,12 +856,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>AFORE-MoTP-Stat</t>
+          <t>AFISH-MoTP-Stat</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AGR_AFORE_DMD</t>
+          <t>AGR_AFISH_DMD</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>AFORE-OTH</t>
+          <t>AFISH-OTH</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AGR_AFORE_DMD</t>
+          <t>AGR_AFISH_DMD</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -910,12 +910,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>AFORE-PH</t>
+          <t>AFISH-RF-RFGR</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AGR_AFORE_DMD</t>
+          <t>AGR_AFISH_DMD</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -937,12 +937,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>AHORT-IRG</t>
+          <t>AFORE-Bike-MoTP-Mob</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AGR_AHORT_DMD</t>
+          <t>AGR_AFORE_DMD</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -964,12 +964,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>AHORT-LT</t>
+          <t>AFORE-Boiler-PH</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AGR_AHORT_DMD</t>
+          <t>AGR_AFORE_DMD</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>AHORT-MoTP-Mob</t>
+          <t>AFORE-CY-MoTP-Mob</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AGR_AHORT_DMD</t>
+          <t>AGR_AFORE_DMD</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1018,12 +1018,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>AHORT-MoTP-Stat</t>
+          <t>AFORE-GB-MoTP-Mob</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AGR_AHORT_DMD</t>
+          <t>AGR_AFORE_DMD</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1045,12 +1045,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>AINDC-LT</t>
+          <t>AFORE-LT</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AGR_AINDC_DMD</t>
+          <t>AGR_AFORE_DMD</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>AINDC-MoTP-Stat</t>
+          <t>AFORE-MoTP-Stat</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AGR_AINDC_DMD</t>
+          <t>AGR_AFORE_DMD</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1099,12 +1099,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>AINDC-SH</t>
+          <t>AFORE-OTH</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AGR_AINDC_DMD</t>
+          <t>AGR_AFORE_DMD</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ALIVE-IRG</t>
+          <t>AHORT-IRG</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>AGR_ALIVE_DMD</t>
+          <t>AGR_AHORT_DMD</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1153,12 +1153,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ALIVE-LT</t>
+          <t>AHORT-LT</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AGR_ALIVE_DMD</t>
+          <t>AGR_AHORT_DMD</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1180,12 +1180,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ALIVE-MoTP-Mob</t>
+          <t>AHORT-MTr-MoTP-Mob</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>AGR_ALIVE_DMD</t>
+          <t>AGR_AHORT_DMD</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1207,12 +1207,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>AOTH-MoTP-Stat</t>
+          <t>AHORT-MoTP-Stat</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>AGR_AOTH_DMD</t>
+          <t>AGR_AHORT_DMD</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>AOTH-PH</t>
+          <t>AHORT-Trac-MoTP-Mob</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>AGR_AOTH_DMD</t>
+          <t>AGR_AHORT_DMD</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1261,12 +1261,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>AOTH-SH</t>
+          <t>AHORT-Uti-MoTP-Mob</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>AGR_AOTH_DMD</t>
+          <t>AGR_AHORT_DMD</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CHEM-BOILR-PH_HIGH</t>
+          <t>AINDC-Boiler-SH</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>IND_CHEM_DMD</t>
+          <t>AGR_AINDC_DMD</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1315,12 +1315,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CHEM-BURNR-PH_HIGH</t>
+          <t>AINDC-HEATX-SH</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>IND_CHEM_DMD</t>
+          <t>AGR_AINDC_DMD</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1342,12 +1342,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CHEM-ELCTR-ELCTR</t>
+          <t>AINDC-LT</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>IND_CHEM_DMD</t>
+          <t>AGR_AINDC_DMD</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CHEM-FURNC-PH_HIGH</t>
+          <t>AINDC-MoTP-Stat</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>IND_CHEM_DMD</t>
+          <t>AGR_AINDC_DMD</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1396,12 +1396,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CHEM-FURNC-PH_INT</t>
+          <t>ALIVE-Bike-MoTP-Mob</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>IND_CHEM_DMD</t>
+          <t>AGR_ALIVE_DMD</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CHEM-HEATR-PH_INT</t>
+          <t>ALIVE-IRG</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>IND_CHEM_DMD</t>
+          <t>AGR_ALIVE_DMD</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CHEM-LIGHT-LIGHT</t>
+          <t>ALIVE-LT</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>IND_CHEM_DMD</t>
+          <t>AGR_ALIVE_DMD</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1477,12 +1477,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CHEM-MOTOR-MTV_STA</t>
+          <t>ALIVE-MTr-MoTP-Mob</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>IND_CHEM_DMD</t>
+          <t>AGR_ALIVE_DMD</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CHEM-SH_LOW</t>
+          <t>ALIVE-Trac-MoTP-Mob</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>IND_CHEM_DMD</t>
+          <t>AGR_ALIVE_DMD</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1531,12 +1531,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CNST-ELCTR-ELCTR</t>
+          <t>ALIVE-Uti-MoTP-Mob</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>IND_CNST_DMD</t>
+          <t>AGR_ALIVE_DMD</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1558,12 +1558,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CNST-ENGIN-MTV_STA</t>
+          <t>AOTH-Furnace-PH</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>IND_CNST_DMD</t>
+          <t>AGR_AOTH_DMD</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CNST-ICENG-MTV_MOB</t>
+          <t>AOTH-MoTP-Stat</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>IND_CNST_DMD</t>
+          <t>AGR_AOTH_DMD</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CNST-LIGHT-LIGHT</t>
+          <t>AOTH-PH</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>IND_CNST_DMD</t>
+          <t>AGR_AOTH_DMD</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1639,12 +1639,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CNST-MOTOR-MTV_STA</t>
+          <t>AOTH-SH</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>IND_CNST_DMD</t>
+          <t>AGR_AOTH_DMD</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1666,12 +1666,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CNST-SH_LOW</t>
+          <t>CHEM-BOILR-PH_HIGH</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>IND_CNST_DMD</t>
+          <t>IND_CHEM_DMD</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1693,12 +1693,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>C_DATA-LT</t>
+          <t>CHEM-BURNR-PH_HIGH</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>COM_DATA_DMD</t>
+          <t>IND_CHEM_DMD</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1720,12 +1720,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>C_DATA-OTH</t>
+          <t>CHEM-ELCTR-ELCTR</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>COM_DATA_DMD</t>
+          <t>IND_CHEM_DMD</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1747,12 +1747,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>C_DATA-SC</t>
+          <t>CHEM-FURNC-PH_HIGH</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>COM_DATA_DMD</t>
+          <t>IND_CHEM_DMD</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>C_EDU-LT</t>
+          <t>CHEM-FURNC-PH_INT</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>POP</t>
+          <t>IND_CHEM_DMD</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>C_EDU-MPM</t>
+          <t>CHEM-HEATR-PH_INT</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>POP</t>
+          <t>IND_CHEM_DMD</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>C_EDU-MPS</t>
+          <t>CHEM-LIGHT-LIGHT</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>POP</t>
+          <t>IND_CHEM_DMD</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1855,12 +1855,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>C_EDU-OTH</t>
+          <t>CHEM-MOTOR-MTV_STA</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>POP</t>
+          <t>IND_CHEM_DMD</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>C_EDU-RF</t>
+          <t>CHEM-SH_LOW</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>POP</t>
+          <t>IND_CHEM_DMD</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>C_EDU-SC</t>
+          <t>CNST-ELCTR-ELCTR</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>POP</t>
+          <t>IND_CNST_DMD</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>C_EDU-SH</t>
+          <t>CNST-ENGIN-MTV_STA</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>POP</t>
+          <t>IND_CNST_DMD</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1963,12 +1963,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>C_EDU-WH</t>
+          <t>CNST-ICENG-MTV_MOB</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>POP</t>
+          <t>IND_CNST_DMD</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -1990,12 +1990,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>C_HLTH-LT</t>
+          <t>CNST-LIGHT-LIGHT</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>POP</t>
+          <t>IND_CNST_DMD</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2017,12 +2017,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>C_HLTH-MPM</t>
+          <t>CNST-MOTOR-MTV_STA</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>POP</t>
+          <t>IND_CNST_DMD</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2044,12 +2044,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>C_HLTH-MPS</t>
+          <t>CNST-SH_LOW</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>POP</t>
+          <t>IND_CNST_DMD</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2071,12 +2071,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>C_HLTH-OTH</t>
+          <t>C_DATA-LT</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>POP</t>
+          <t>COM_DATA_DMD</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2098,12 +2098,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>C_HLTH-PH</t>
+          <t>C_DATA-OTH</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>POP</t>
+          <t>COM_DATA_DMD</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>C_HLTH-RF</t>
+          <t>C_DATA-SC</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>POP</t>
+          <t>COM_DATA_DMD</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>C_HLTH-SC</t>
+          <t>C_EDU-Boiler-SH</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2179,7 +2179,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>C_HLTH-SH</t>
+          <t>C_EDU-Boiler-WH</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>C_HLTH-WH</t>
+          <t>C_EDU-Burner-SH</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>C_OFFC-LT</t>
+          <t>C_EDU-LT</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>GDP</t>
+          <t>POP</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>C_OFFC-MPM</t>
+          <t>C_EDU-MPM</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>GDP</t>
+          <t>POP</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>C_OFFC-MPS</t>
+          <t>C_EDU-MPS</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>GDP</t>
+          <t>POP</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2314,12 +2314,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>C_OFFC-OTH</t>
+          <t>C_EDU-OTH</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>GDP</t>
+          <t>POP</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>C_OFFC-SC</t>
+          <t>C_EDU-RF</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>GDP</t>
+          <t>POP</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2368,12 +2368,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>C_OFFC-SH</t>
+          <t>C_EDU-RH-SH</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>GDP</t>
+          <t>POP</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2395,12 +2395,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>C_OFFC-WH</t>
+          <t>C_EDU-SC</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>GDP</t>
+          <t>POP</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2422,12 +2422,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>C_OTH-LT</t>
+          <t>C_EDU-SH</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Constant</t>
+          <t>POP</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>C_OTH-MPM</t>
+          <t>C_EDU-WH</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Constant</t>
+          <t>POP</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2476,12 +2476,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>C_OTH-MPS</t>
+          <t>C_HLTH-Boiler-PH</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Constant</t>
+          <t>POP</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>C_OTH-OTH</t>
+          <t>C_HLTH-Boiler-SH</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Constant</t>
+          <t>POP</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>C_OTH-PUMP</t>
+          <t>C_HLTH-Boiler-WH</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Constant</t>
+          <t>POP</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -2557,12 +2557,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>C_OTH-SC</t>
+          <t>C_HLTH-LT</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Constant</t>
+          <t>POP</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>C_OTH-SH</t>
+          <t>C_HLTH-MPM</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Constant</t>
+          <t>POP</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>C_OTH-WH</t>
+          <t>C_HLTH-MPS</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Constant</t>
+          <t>POP</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>C_WSR-CK</t>
+          <t>C_HLTH-OTH</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>GDP</t>
+          <t>POP</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -2665,12 +2665,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>C_WSR-LT</t>
+          <t>C_HLTH-RF</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>GDP</t>
+          <t>POP</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -2692,12 +2692,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>C_WSR-MPM</t>
+          <t>C_HLTH-RH-PH</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>GDP</t>
+          <t>POP</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>C_WSR-MPS</t>
+          <t>C_HLTH-RH-SH</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>GDP</t>
+          <t>POP</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -2746,12 +2746,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>C_WSR-OTH</t>
+          <t>C_HLTH-SC</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>GDP</t>
+          <t>POP</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -2773,12 +2773,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>C_WSR-RF</t>
+          <t>C_HLTH-SH</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>GDP</t>
+          <t>POP</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -2800,12 +2800,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>C_WSR-SC</t>
+          <t>C_HLTH-WH</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>GDP</t>
+          <t>POP</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>C_WSR-SH</t>
+          <t>C_OFFC-Boiler-SH</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -2854,7 +2854,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>C_WSR-WH</t>
+          <t>C_OFFC-Boiler-WH</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -2881,12 +2881,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>DARY-ACOMP-COMP_AIR</t>
+          <t>C_OFFC-Burner-SH</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>IND_DARY_DMD</t>
+          <t>GDP</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -2908,12 +2908,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>DARY-BOILR-PH_INT</t>
+          <t>C_OFFC-LT</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>IND_DARY_DMD</t>
+          <t>GDP</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -2935,12 +2935,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>DARY-BOILR-PH_LOW</t>
+          <t>C_OFFC-MPM</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>IND_DARY_DMD</t>
+          <t>GDP</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>DARY-BOILR-WH_LOW</t>
+          <t>C_OFFC-MPS</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>IND_DARY_DMD</t>
+          <t>GDP</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>DARY-FAN-FAN</t>
+          <t>C_OFFC-OTH</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>IND_DARY_DMD</t>
+          <t>GDP</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -3016,12 +3016,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>DARY-FRIDG-FRIDG</t>
+          <t>C_OFFC-RH-SH</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>IND_DARY_DMD</t>
+          <t>GDP</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -3043,12 +3043,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>DARY-HEATX-PH_INT</t>
+          <t>C_OFFC-SC</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>IND_DARY_DMD</t>
+          <t>GDP</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -3070,12 +3070,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>DARY-HEATX-WH_LOW</t>
+          <t>C_OFFC-SH</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>IND_DARY_DMD</t>
+          <t>GDP</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -3097,12 +3097,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>DARY-LIGHT-LIGHT</t>
+          <t>C_OFFC-WH</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>IND_DARY_DMD</t>
+          <t>GDP</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -3124,12 +3124,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>DARY-MOTOR-MTV_STA</t>
+          <t>C_OTH-Boiler-SH</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>IND_DARY_DMD</t>
+          <t>Constant</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>DARY-PUMP-PUMP</t>
+          <t>C_OTH-Boiler-WH</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>IND_DARY_DMD</t>
+          <t>Constant</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -3178,12 +3178,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>DARY-SH_LOW</t>
+          <t>C_OTH-Burner-SH</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>IND_DARY_DMD</t>
+          <t>Constant</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>DD-CH_INT</t>
+          <t>C_OTH-LT</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>POP</t>
+          <t>Constant</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -3232,12 +3232,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>DD-C_DRY</t>
+          <t>C_OTH-MPM</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>POP</t>
+          <t>Constant</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>DD-C_WASH</t>
+          <t>C_OTH-MPS</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>POP</t>
+          <t>Constant</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -3286,12 +3286,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>DD-D_WASH</t>
+          <t>C_OTH-OTH</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>POP</t>
+          <t>Constant</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>DD-ELCTR</t>
+          <t>C_OTH-PUMP</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>POP</t>
+          <t>Constant</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -3340,12 +3340,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>DD-FRIDG</t>
+          <t>C_OTH-RH-SH</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>POP</t>
+          <t>Constant</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -3367,12 +3367,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>DD-LIGHT</t>
+          <t>C_OTH-SC</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>POP</t>
+          <t>Constant</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -3394,12 +3394,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>DD-MTV_MOB</t>
+          <t>C_OTH-SH</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>POP</t>
+          <t>Constant</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -3421,12 +3421,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>DD-S_COOL</t>
+          <t>C_OTH-WH</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>POP</t>
+          <t>Constant</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -3448,12 +3448,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>DD-S_HEAT</t>
+          <t>C_WSR-Boiler-SH</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>POP</t>
+          <t>GDP</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>DD-WH_LOW</t>
+          <t>C_WSR-Boiler-WH</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>POP</t>
+          <t>GDP</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -3502,12 +3502,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>FOOD-ACOMP-COMP_AIR</t>
+          <t>C_WSR-Burner-SH</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>IND_FOOD_DMD</t>
+          <t>GDP</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>FOOD-BOILR-PH_INT</t>
+          <t>C_WSR-CK</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>IND_FOOD_DMD</t>
+          <t>GDP</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -3556,12 +3556,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>FOOD-BOILR-PH_LOW</t>
+          <t>C_WSR-LT</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>IND_FOOD_DMD</t>
+          <t>GDP</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -3583,12 +3583,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>FOOD-BOILR-WH_LOW</t>
+          <t>C_WSR-MPM</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>IND_FOOD_DMD</t>
+          <t>GDP</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>FOOD-ELCTR-ELCTR</t>
+          <t>C_WSR-MPS</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>IND_FOOD_DMD</t>
+          <t>GDP</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>FOOD-FRIDG-FRIDG</t>
+          <t>C_WSR-OTH</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>IND_FOOD_DMD</t>
+          <t>GDP</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>FOOD-IOVEN-CH_INT</t>
+          <t>C_WSR-RF</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>IND_FOOD_DMD</t>
+          <t>GDP</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -3691,12 +3691,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>FOOD-LIGHT-LIGHT</t>
+          <t>C_WSR-RH-SH</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>IND_FOOD_DMD</t>
+          <t>GDP</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>FOOD-MOTOR-MTV_STA</t>
+          <t>C_WSR-SC</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>IND_FOOD_DMD</t>
+          <t>GDP</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>FOOD-PUMP-PUMP</t>
+          <t>C_WSR-SH</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>IND_FOOD_DMD</t>
+          <t>GDP</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>FOOD-SH_LOW</t>
+          <t>C_WSR-WH</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>IND_FOOD_DMD</t>
+          <t>GDP</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -3799,12 +3799,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>JD-CH_INT</t>
+          <t>DARY-ACOMP-COMP_AIR</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>POP</t>
+          <t>IND_DARY_DMD</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -3826,12 +3826,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>JD-C_DRY</t>
+          <t>DARY-BOILR-PH_INT</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>POP</t>
+          <t>IND_DARY_DMD</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -3853,12 +3853,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>JD-C_WASH</t>
+          <t>DARY-BOILR-PH_LOW</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>POP</t>
+          <t>IND_DARY_DMD</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -3880,12 +3880,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>JD-D_WASH</t>
+          <t>DARY-BOILR-WH_LOW</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>POP</t>
+          <t>IND_DARY_DMD</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>JD-ELCTR</t>
+          <t>DARY-FAN-FAN</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>POP</t>
+          <t>IND_DARY_DMD</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -3934,12 +3934,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>JD-FRIDG</t>
+          <t>DARY-FRIDG-FRIDG</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>POP</t>
+          <t>IND_DARY_DMD</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>JD-LIGHT</t>
+          <t>DARY-HEATX-PH_INT</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>POP</t>
+          <t>IND_DARY_DMD</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>JD-MTV_MOB</t>
+          <t>DARY-HEATX-WH_LOW</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>POP</t>
+          <t>IND_DARY_DMD</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -4015,12 +4015,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>JD-S_COOL</t>
+          <t>DARY-LIGHT-LIGHT</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>POP</t>
+          <t>IND_DARY_DMD</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -4042,12 +4042,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>JD-S_HEAT</t>
+          <t>DARY-MOTOR-MTV_STA</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>POP</t>
+          <t>IND_DARY_DMD</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>JD-WH_LOW</t>
+          <t>DARY-PUMP-PUMP</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>POP</t>
+          <t>IND_DARY_DMD</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -4096,12 +4096,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>MEAT-BOILR-PH_INT</t>
+          <t>DARY-SH_LOW</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>IND_MEAT_DMD</t>
+          <t>IND_DARY_DMD</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>MEAT-BOILR-WH_LOW</t>
+          <t>DD-CH_INT</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>IND_MEAT_DMD</t>
+          <t>POP</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -4150,12 +4150,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>MEAT-FRIDG-FRIDG</t>
+          <t>DD-C_DRY</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>IND_MEAT_DMD</t>
+          <t>POP</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>MEAT-HEATR-WH_LOW</t>
+          <t>DD-C_WASH</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>IND_MEAT_DMD</t>
+          <t>POP</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>MEAT-LIGHT-LIGHT</t>
+          <t>DD-D_WASH</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>IND_MEAT_DMD</t>
+          <t>POP</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -4231,12 +4231,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>MEAT-MOTOR-MTV_STA</t>
+          <t>DD-ELCTR</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>IND_MEAT_DMD</t>
+          <t>POP</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -4258,12 +4258,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>METH-FDSTK-FDSTK</t>
+          <t>DD-FRIDG</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>IND_METH_DMD</t>
+          <t>POP</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>METH-REFRM-PH_HIGH</t>
+          <t>DD-LIGHT</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>IND_METH_DMD</t>
+          <t>POP</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -4312,12 +4312,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>MINE-BOILR-PH_INT</t>
+          <t>DD-MTV_MOB</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>IND_MINE_DMD</t>
+          <t>POP</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>MINE-ELCTR-ELCTR</t>
+          <t>DD-S_COOL</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>IND_MINE_DMD</t>
+          <t>POP</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -4366,12 +4366,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>MINE-ENGIN-MTV_STA</t>
+          <t>DD-S_HEAT</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>IND_MINE_DMD</t>
+          <t>POP</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -4393,12 +4393,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>MINE-ICENG-MTV_MOB</t>
+          <t>DD-WH_LOW</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>IND_MINE_DMD</t>
+          <t>POP</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>MINE-LIGHT-LIGHT</t>
+          <t>FOOD-ACOMP-COMP_AIR</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>IND_MINE_DMD</t>
+          <t>IND_FOOD_DMD</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>MINE-MOTOR-MTV_STA</t>
+          <t>FOOD-BOILR-PH_INT</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>IND_MINE_DMD</t>
+          <t>IND_FOOD_DMD</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -4474,12 +4474,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>MNRL-BOILR-PH_INT</t>
+          <t>FOOD-BOILR-PH_LOW</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>IND_MNRL_DMD</t>
+          <t>IND_FOOD_DMD</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>MNRL-BOILR-PH_LOW</t>
+          <t>FOOD-BOILR-WH_LOW</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>IND_MNRL_DMD</t>
+          <t>IND_FOOD_DMD</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -4528,12 +4528,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>MNRL-FURNC-PH_HIGH</t>
+          <t>FOOD-ELCTR-ELCTR</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>IND_MNRL_DMD</t>
+          <t>IND_FOOD_DMD</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>MNRL-FURNC-PH_INT</t>
+          <t>FOOD-FRIDG-FRIDG</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>IND_MNRL_DMD</t>
+          <t>IND_FOOD_DMD</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>MNRL-LIGHT-LIGHT</t>
+          <t>FOOD-IOVEN-CH_INT</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>IND_MNRL_DMD</t>
+          <t>IND_FOOD_DMD</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>MNRL-MOTOR-MTV_STA</t>
+          <t>FOOD-LIGHT-LIGHT</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>IND_MNRL_DMD</t>
+          <t>IND_FOOD_DMD</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -4636,12 +4636,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>MNRL-PUMP-PUMP</t>
+          <t>FOOD-MOTOR-MTV_STA</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>IND_MNRL_DMD</t>
+          <t>IND_FOOD_DMD</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>OTHR-BOILR-PH_INT</t>
+          <t>FOOD-PUMP-PUMP</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Constant</t>
+          <t>IND_FOOD_DMD</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -4690,12 +4690,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>OTHR-BOILR-PH_LOW</t>
+          <t>FOOD-SH_LOW</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Constant</t>
+          <t>IND_FOOD_DMD</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -4717,12 +4717,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>OTHR-EFURNC-PH_HIGH</t>
+          <t>JD-CH_INT</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Constant</t>
+          <t>POP</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -4744,12 +4744,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>OTHR-ELCTR-ELCTR</t>
+          <t>JD-C_DRY</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Constant</t>
+          <t>POP</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>OTHR-FURNC-PH_HIGH</t>
+          <t>JD-C_WASH</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Constant</t>
+          <t>POP</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>OTHR-HEATR-PH_INT</t>
+          <t>JD-D_WASH</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Constant</t>
+          <t>POP</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>OTHR-HEATR-PH_LOW</t>
+          <t>JD-ELCTR</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Constant</t>
+          <t>POP</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -4852,12 +4852,12 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>OTHR-ICENG-MTV_MOB</t>
+          <t>JD-FRIDG</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Constant</t>
+          <t>POP</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -4879,12 +4879,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>OTHR-LIGHT-LIGHT</t>
+          <t>JD-LIGHT</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Constant</t>
+          <t>POP</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -4906,12 +4906,12 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>OTHR-MOTOR-MTV_STA</t>
+          <t>JD-MTV_MOB</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Constant</t>
+          <t>POP</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -4933,12 +4933,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>OTHR-PUMP-PUMP</t>
+          <t>JD-S_COOL</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Constant</t>
+          <t>POP</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -4960,12 +4960,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>OTHR-SH_LOW</t>
+          <t>JD-S_HEAT</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Constant</t>
+          <t>POP</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -4987,12 +4987,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>PULP-ACOMP-COMP_AIR</t>
+          <t>JD-WH_LOW</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>IND_PULP_DMD</t>
+          <t>POP</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -5014,12 +5014,12 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>PULP-BOILR-PH_INT</t>
+          <t>MEAT-BOILR-PH_INT</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>IND_PULP_DMD</t>
+          <t>IND_MEAT_DMD</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -5041,12 +5041,12 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>PULP-BURNR-PH_LOW</t>
+          <t>MEAT-BOILR-WH_LOW</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>IND_PULP_DMD</t>
+          <t>IND_MEAT_DMD</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -5068,12 +5068,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>PULP-ELCTR-ELCTR</t>
+          <t>MEAT-FRIDG-FRIDG</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>IND_PULP_DMD</t>
+          <t>IND_MEAT_DMD</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>PULP-FAN-FAN</t>
+          <t>MEAT-HEATR-WH_LOW</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>IND_PULP_DMD</t>
+          <t>IND_MEAT_DMD</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>PULP-FURNC-PH_HIGH</t>
+          <t>MEAT-LIGHT-LIGHT</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>IND_PULP_DMD</t>
+          <t>IND_MEAT_DMD</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -5149,12 +5149,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>PULP-HEATX-PH_INT</t>
+          <t>MEAT-MOTOR-MTV_STA</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>IND_PULP_DMD</t>
+          <t>IND_MEAT_DMD</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -5176,12 +5176,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>PULP-LIGHT-LIGHT</t>
+          <t>METH-FDSTK-FDSTK</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>IND_PULP_DMD</t>
+          <t>IND_METH_DMD</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>PULP-MOTOR-MTV_STA</t>
+          <t>METH-REFRM-PH_HIGH</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>IND_PULP_DMD</t>
+          <t>IND_METH_DMD</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -5230,12 +5230,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>PULP-PUMP-PUMP</t>
+          <t>MINE-BOILR-PH_INT</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>IND_PULP_DMD</t>
+          <t>IND_MINE_DMD</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -5257,12 +5257,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>PULP-REFIN-REFIN</t>
+          <t>MINE-ELCTR-ELCTR</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>IND_PULP_DMD</t>
+          <t>IND_MINE_DMD</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -5284,12 +5284,12 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>PULP-SH_LOW</t>
+          <t>MINE-ENGIN-MTV_STA</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>IND_PULP_DMD</t>
+          <t>IND_MINE_DMD</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -5311,12 +5311,12 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>STEEL-BOILR-WH_LOW</t>
+          <t>MINE-ICENG-MTV_MOB</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>IND_STEEL_DMD</t>
+          <t>IND_MINE_DMD</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -5338,12 +5338,12 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>STEEL-BURNR-PH_INT</t>
+          <t>MINE-LIGHT-LIGHT</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>IND_STEEL_DMD</t>
+          <t>IND_MINE_DMD</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>STEEL-EFURNC-ISTEEL</t>
+          <t>MINE-MOTOR-MTV_STA</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>IND_STEEL_DMD</t>
+          <t>IND_MINE_DMD</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -5392,12 +5392,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>STEEL-ELCTR-ELCTR</t>
+          <t>MNRL-BOILR-PH_INT</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>IND_STEEL_DMD</t>
+          <t>IND_MNRL_DMD</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -5419,12 +5419,12 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>STEEL-FDSTK-FDSTK</t>
+          <t>MNRL-BOILR-PH_LOW</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>IND_STEEL_EAF_DMD</t>
+          <t>IND_MNRL_DMD</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>STEEL-FRIDG-FRIDG</t>
+          <t>MNRL-FURNC-PH_HIGH</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>IND_STEEL_DMD</t>
+          <t>IND_MNRL_DMD</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -5473,12 +5473,12 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>STEEL-FURNC-ISTEEL</t>
+          <t>MNRL-FURNC-PH_INT</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>IND_STEEL_EAF_DMD</t>
+          <t>IND_MNRL_DMD</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -5500,12 +5500,12 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>STEEL-FURNC-PH_HIGH</t>
+          <t>MNRL-LIGHT-LIGHT</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>IND_STEEL_DMD</t>
+          <t>IND_MNRL_DMD</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -5527,12 +5527,12 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>STEEL-HEATR-PH_LOW</t>
+          <t>MNRL-MOTOR-MTV_STA</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>IND_STEEL_DMD</t>
+          <t>IND_MNRL_DMD</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>STEEL-IOVEN-PH_HIGH</t>
+          <t>MNRL-PUMP-PUMP</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>IND_STEEL_DMD</t>
+          <t>IND_MNRL_DMD</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -5581,12 +5581,12 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>STEEL-LIGHT-LIGHT</t>
+          <t>OTHR-BOILR-PH_INT</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>IND_STEEL_DMD</t>
+          <t>Constant</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>STEEL-MOTOR-ISTEEL</t>
+          <t>OTHR-BOILR-PH_LOW</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>IND_STEEL_EAF_DMD</t>
+          <t>Constant</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -5635,12 +5635,12 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>STEEL-MOTOR-MTV_STA</t>
+          <t>OTHR-EFURNC-PH_HIGH</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>IND_STEEL_DMD</t>
+          <t>Constant</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -5662,12 +5662,12 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>T_C_Car</t>
+          <t>OTHR-ELCTR-ELCTR</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>TRA_LCV_DEM</t>
+          <t>Constant</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -5689,12 +5689,12 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>T_F_DSHIP</t>
+          <t>OTHR-FURNC-PH_HIGH</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>GDP</t>
+          <t>Constant</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -5716,12 +5716,12 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>T_F_HTrk</t>
+          <t>OTHR-HEATR-PH_INT</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>TRA_HTRK_DEM</t>
+          <t>Constant</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -5743,12 +5743,12 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>T_F_ISHIP</t>
+          <t>OTHR-HEATR-PH_LOW</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>GDP</t>
+          <t>Constant</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>T_F_LTrk</t>
+          <t>OTHR-ICENG-MTV_MOB</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>TRA_LTRK_DEM</t>
+          <t>Constant</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -5797,12 +5797,12 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>T_F_MTrk</t>
+          <t>OTHR-LIGHT-LIGHT</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>TRA_MTRK_DEM</t>
+          <t>Constant</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>T_F_Rail</t>
+          <t>OTHR-MOTOR-MTV_STA</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>GDP</t>
+          <t>Constant</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -5851,12 +5851,12 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>T_O_JET</t>
+          <t>OTHR-PUMP-PUMP</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>POP</t>
+          <t>Constant</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -5878,12 +5878,12 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>T_O_JET_Int</t>
+          <t>OTHR-SH_LOW</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>POP</t>
+          <t>Constant</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -5905,12 +5905,12 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>T_P_Bus</t>
+          <t>PULP-ACOMP-COMP_AIR</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>TRA_BUS_DEM</t>
+          <t>IND_PULP_DMD</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>T_P_Car</t>
+          <t>PULP-BOILR-PH_INT</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>TRA_LPV_DEM</t>
+          <t>IND_PULP_DMD</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -5959,12 +5959,12 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>T_P_Mcy</t>
+          <t>PULP-BURNR-PH_LOW</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>TRA_MCY_DEM</t>
+          <t>IND_PULP_DMD</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -5986,12 +5986,12 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>T_P_Rail</t>
+          <t>PULP-ELCTR-ELCTR</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>GDP</t>
+          <t>IND_PULP_DMD</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>UREA-COMPR-MTV_STA</t>
+          <t>PULP-FAN-FAN</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>IND_UREA_DMD</t>
+          <t>IND_PULP_DMD</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -6040,12 +6040,12 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>UREA-FDSTK-FDSTK</t>
+          <t>PULP-FURNC-PH_HIGH</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>IND_UREA_DMD</t>
+          <t>IND_PULP_DMD</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -6067,12 +6067,12 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>UREA-REFRM-PH_HIGH</t>
+          <t>PULP-HEATX-PH_INT</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>IND_UREA_DMD</t>
+          <t>IND_PULP_DMD</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -6094,12 +6094,12 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>WOOD-ACOMP-COMP_AIR</t>
+          <t>PULP-LIGHT-LIGHT</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>IND_WOOD_DMD</t>
+          <t>IND_PULP_DMD</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>WOOD-BOILR-PH_INT</t>
+          <t>PULP-MOTOR-MTV_STA</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>IND_WOOD_DMD</t>
+          <t>IND_PULP_DMD</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>WOOD-BOILR-PH_LOW</t>
+          <t>PULP-PUMP-PUMP</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>IND_WOOD_DMD</t>
+          <t>IND_PULP_DMD</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -6175,12 +6175,12 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>WOOD-BURNR-PH_INT</t>
+          <t>PULP-REFIN-REFIN</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>IND_WOOD_DMD</t>
+          <t>IND_PULP_DMD</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -6202,12 +6202,12 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>WOOD-ELCTR-ELCTR</t>
+          <t>PULP-SH_LOW</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>IND_WOOD_DMD</t>
+          <t>IND_PULP_DMD</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -6229,12 +6229,12 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>WOOD-FAN-FAN</t>
+          <t>STEEL-BOILR-WH_LOW</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>IND_WOOD_DMD</t>
+          <t>IND_STEEL_DMD</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -6256,12 +6256,12 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>WOOD-FURNC-PH_LOW</t>
+          <t>STEEL-BURNR-PH_INT</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>IND_WOOD_DMD</t>
+          <t>IND_STEEL_DMD</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -6283,12 +6283,12 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>WOOD-HEATX-PH_INT</t>
+          <t>STEEL-EFURNC-ISTEEL</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>IND_WOOD_DMD</t>
+          <t>IND_STEEL_DMD</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -6310,12 +6310,12 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>WOOD-HPPH-PH_LOW</t>
+          <t>STEEL-ELCTR-ELCTR</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>IND_WOOD_DMD</t>
+          <t>IND_STEEL_DMD</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -6337,12 +6337,12 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>WOOD-LIGHT-LIGHT</t>
+          <t>STEEL-FDSTK-FDSTK</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>IND_WOOD_DMD</t>
+          <t>IND_STEEL_EAF_DMD</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -6364,12 +6364,12 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>WOOD-MOTOR-MTV_STA</t>
+          <t>STEEL-FRIDG-FRIDG</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>IND_WOOD_DMD</t>
+          <t>IND_STEEL_DMD</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>WOOD-PUMP-PUMP</t>
+          <t>STEEL-FURNC-ISTEEL</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>IND_WOOD_DMD</t>
+          <t>IND_STEEL_EAF_DMD</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -6418,12 +6418,12 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>WOOD-REFIN-REFIN</t>
+          <t>STEEL-FURNC-PH_HIGH</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>IND_WOOD_DMD</t>
+          <t>IND_STEEL_DMD</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -6440,17 +6440,17 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NI</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>ADCF-IRG</t>
+          <t>STEEL-HEATR-PH_LOW</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>AGR_ADCF_DMD</t>
+          <t>IND_STEEL_DMD</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -6467,17 +6467,17 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NI</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>ADCF-LT</t>
+          <t>STEEL-IOVEN-PH_HIGH</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>AGR_ADCF_DMD</t>
+          <t>IND_STEEL_DMD</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -6494,17 +6494,17 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NI</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>ADCF-MoTP-Mob</t>
+          <t>STEEL-LIGHT-LIGHT</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>AGR_ADCF_DMD</t>
+          <t>IND_STEEL_DMD</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -6521,17 +6521,17 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NI</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>ADCF-MoTP-Stat</t>
+          <t>STEEL-MOTOR-ISTEEL</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>AGR_ADCF_DMD</t>
+          <t>IND_STEEL_EAF_DMD</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -6548,17 +6548,17 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NI</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>ADCF-PUMP</t>
+          <t>STEEL-MOTOR-MTV_STA</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>AGR_ADCF_DMD</t>
+          <t>IND_STEEL_DMD</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -6575,17 +6575,17 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NI</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>ADCF-RFGR</t>
+          <t>T_C_Car</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>AGR_ADCF_DMD</t>
+          <t>TRA_LCV_DEM</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -6602,17 +6602,17 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NI</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>ADCF-WH</t>
+          <t>T_F_DSHIP</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>AGR_ADCF_DMD</t>
+          <t>GDP</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -6629,17 +6629,17 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NI</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>AFISH-LT</t>
+          <t>T_F_HTrk</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>AGR_AFISH_DMD</t>
+          <t>TRA_HTRK_DEM</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -6656,17 +6656,17 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NI</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>AFISH-MoTP-Mob</t>
+          <t>T_F_ISHIP</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>AGR_AFISH_DMD</t>
+          <t>GDP</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -6683,17 +6683,17 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NI</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>AFISH-MoTP-Stat</t>
+          <t>T_F_LTrk</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>AGR_AFISH_DMD</t>
+          <t>TRA_LTRK_DEM</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -6710,17 +6710,17 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NI</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>AFISH-OTH</t>
+          <t>T_F_MTrk</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>AGR_AFISH_DMD</t>
+          <t>TRA_MTRK_DEM</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -6737,17 +6737,17 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NI</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>AFISH-RFGR</t>
+          <t>T_F_Rail</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>AGR_AFISH_DMD</t>
+          <t>GDP</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -6764,17 +6764,17 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NI</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>AFORE-LT</t>
+          <t>T_O_JET</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>AGR_AFORE_DMD</t>
+          <t>POP</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -6791,17 +6791,17 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NI</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>AFORE-MoTP-Mob</t>
+          <t>T_O_JET_Int</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>AGR_AFORE_DMD</t>
+          <t>POP</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -6818,17 +6818,17 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NI</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>AFORE-MoTP-Stat</t>
+          <t>T_P_Bus</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>AGR_AFORE_DMD</t>
+          <t>TRA_BUS_DEM</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -6845,17 +6845,17 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NI</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>AFORE-OTH</t>
+          <t>T_P_Car</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>AGR_AFORE_DMD</t>
+          <t>TRA_LPV_DEM</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -6872,17 +6872,17 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NI</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>AHORT-IRG</t>
+          <t>T_P_Mcy</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>AGR_AHORT_DMD</t>
+          <t>TRA_MCY_DEM</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -6899,17 +6899,17 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NI</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>AHORT-LT</t>
+          <t>T_P_Rail</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>AGR_AHORT_DMD</t>
+          <t>GDP</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -6926,17 +6926,17 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NI</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>AHORT-MoTP-Mob</t>
+          <t>UREA-COMPR-MTV_STA</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>AGR_AHORT_DMD</t>
+          <t>IND_UREA_DMD</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -6953,17 +6953,17 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NI</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>AHORT-MoTP-Stat</t>
+          <t>UREA-FDSTK-FDSTK</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>AGR_AHORT_DMD</t>
+          <t>IND_UREA_DMD</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -6980,17 +6980,17 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NI</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>AINDC-LT</t>
+          <t>UREA-REFRM-PH_HIGH</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>AGR_AINDC_DMD</t>
+          <t>IND_UREA_DMD</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -7007,17 +7007,17 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NI</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>AINDC-MoTP-Stat</t>
+          <t>WOOD-ACOMP-COMP_AIR</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>AGR_AINDC_DMD</t>
+          <t>IND_WOOD_DMD</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -7034,17 +7034,17 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NI</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>AINDC-SH</t>
+          <t>WOOD-BOILR-PH_INT</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>AGR_AINDC_DMD</t>
+          <t>IND_WOOD_DMD</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -7061,17 +7061,17 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NI</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>ALIVE-IRG</t>
+          <t>WOOD-BOILR-PH_LOW</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>AGR_ALIVE_DMD</t>
+          <t>IND_WOOD_DMD</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -7088,17 +7088,17 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NI</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>ALIVE-LT</t>
+          <t>WOOD-BURNR-PH_INT</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>AGR_ALIVE_DMD</t>
+          <t>IND_WOOD_DMD</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -7115,17 +7115,17 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NI</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>ALIVE-MoTP-Mob</t>
+          <t>WOOD-ELCTR-ELCTR</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>AGR_ALIVE_DMD</t>
+          <t>IND_WOOD_DMD</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -7142,17 +7142,17 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NI</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>ALUM-EFURNC-PH_HIGH</t>
+          <t>WOOD-FAN-FAN</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>IND_ALUM_DMD</t>
+          <t>IND_WOOD_DMD</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -7169,17 +7169,17 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NI</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>AOTH-MoTP-Stat</t>
+          <t>WOOD-FURNC-PH_LOW</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>AGR_AOTH_DMD</t>
+          <t>IND_WOOD_DMD</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -7196,17 +7196,17 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NI</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>AOTH-PH</t>
+          <t>WOOD-HEATX-PH_INT</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>AGR_AOTH_DMD</t>
+          <t>IND_WOOD_DMD</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -7223,17 +7223,17 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NI</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>AOTH-SH</t>
+          <t>WOOD-HPPH-PH_LOW</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>AGR_AOTH_DMD</t>
+          <t>IND_WOOD_DMD</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -7250,17 +7250,17 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NI</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>CNST-ELCTR-ELCTR</t>
+          <t>WOOD-LIGHT-LIGHT</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>IND_CNST_DMD</t>
+          <t>IND_WOOD_DMD</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -7277,17 +7277,17 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NI</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>CNST-ENGIN-MTV_STA</t>
+          <t>WOOD-MOTOR-MTV_STA</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>IND_CNST_DMD</t>
+          <t>IND_WOOD_DMD</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -7304,17 +7304,17 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NI</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>CNST-ICENG-MTV_MOB</t>
+          <t>WOOD-PUMP-PUMP</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>IND_CNST_DMD</t>
+          <t>IND_WOOD_DMD</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -7331,17 +7331,17 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NI</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>CNST-LIGHT-LIGHT</t>
+          <t>WOOD-REFIN-REFIN</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>IND_CNST_DMD</t>
+          <t>IND_WOOD_DMD</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>CNST-MOTOR-MTV_STA</t>
+          <t>ADCF-Bike-MoTP-Mob</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>IND_CNST_DMD</t>
+          <t>AGR_ADCF_DMD</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>CNST-SH_LOW</t>
+          <t>ADCF-HRECSys-RFGR</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>IND_CNST_DMD</t>
+          <t>AGR_ADCF_DMD</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>C_DATA-LT</t>
+          <t>ADCF-Hreco-WH</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>COM_DATA_DMD</t>
+          <t>AGR_ADCF_DMD</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -7444,12 +7444,12 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>C_DATA-OTH</t>
+          <t>ADCF-IRG</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>COM_DATA_DMD</t>
+          <t>AGR_ADCF_DMD</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -7471,12 +7471,12 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>C_DATA-SC</t>
+          <t>ADCF-LT</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>COM_DATA_DMD</t>
+          <t>AGR_ADCF_DMD</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -7498,12 +7498,12 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>C_EDU-LT</t>
+          <t>ADCF-MTr-MoTP-Mob</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>POP</t>
+          <t>AGR_ADCF_DMD</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>C_EDU-MPM</t>
+          <t>ADCF-MoTP-Stat</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>POP</t>
+          <t>AGR_ADCF_DMD</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -7552,12 +7552,12 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>C_EDU-MPS</t>
+          <t>ADCF-PUMP</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>POP</t>
+          <t>AGR_ADCF_DMD</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -7579,12 +7579,12 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>C_EDU-OTH</t>
+          <t>ADCF-RF-RFGR</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>POP</t>
+          <t>AGR_ADCF_DMD</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -7606,12 +7606,12 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>C_EDU-RF</t>
+          <t>ADCF-Trac-MoTP-Mob</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>POP</t>
+          <t>AGR_ADCF_DMD</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -7633,12 +7633,12 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>C_EDU-SC</t>
+          <t>ADCF-Uti-MoTP-Mob</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>POP</t>
+          <t>AGR_ADCF_DMD</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -7660,12 +7660,12 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>C_EDU-SH</t>
+          <t>ADCF-WH</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>POP</t>
+          <t>AGR_ADCF_DMD</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -7687,12 +7687,12 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>C_EDU-WH</t>
+          <t>AFISH-Boat-MoTP-Mob</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>POP</t>
+          <t>AGR_AFISH_DMD</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -7714,12 +7714,12 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>C_HLTH-LT</t>
+          <t>AFISH-LT</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>POP</t>
+          <t>AGR_AFISH_DMD</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>C_HLTH-MPM</t>
+          <t>AFISH-MoTP-Stat</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>POP</t>
+          <t>AGR_AFISH_DMD</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>C_HLTH-MPS</t>
+          <t>AFISH-OTH</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>POP</t>
+          <t>AGR_AFISH_DMD</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -7795,12 +7795,12 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>C_HLTH-OTH</t>
+          <t>AFISH-RF-RFGR</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>POP</t>
+          <t>AGR_AFISH_DMD</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>C_HLTH-PH</t>
+          <t>AFORE-Bike-MoTP-Mob</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>POP</t>
+          <t>AGR_AFORE_DMD</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -7849,12 +7849,12 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>C_HLTH-RF</t>
+          <t>AFORE-CY-MoTP-Mob</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>POP</t>
+          <t>AGR_AFORE_DMD</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -7876,12 +7876,12 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>C_HLTH-SC</t>
+          <t>AFORE-GB-MoTP-Mob</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>POP</t>
+          <t>AGR_AFORE_DMD</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>C_HLTH-SH</t>
+          <t>AFORE-LT</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>POP</t>
+          <t>AGR_AFORE_DMD</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -7930,12 +7930,12 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>C_HLTH-WH</t>
+          <t>AFORE-MoTP-Stat</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>POP</t>
+          <t>AGR_AFORE_DMD</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -7957,12 +7957,12 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>C_OFFC-LT</t>
+          <t>AFORE-OTH</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>GDP</t>
+          <t>AGR_AFORE_DMD</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -7984,12 +7984,12 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>C_OFFC-MPM</t>
+          <t>AHORT-IRG</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>GDP</t>
+          <t>AGR_AHORT_DMD</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>C_OFFC-MPS</t>
+          <t>AHORT-LT</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>GDP</t>
+          <t>AGR_AHORT_DMD</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -8038,12 +8038,12 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>C_OFFC-OTH</t>
+          <t>AHORT-MTr-MoTP-Mob</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>GDP</t>
+          <t>AGR_AHORT_DMD</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -8065,12 +8065,12 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>C_OFFC-SC</t>
+          <t>AHORT-MoTP-Stat</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>GDP</t>
+          <t>AGR_AHORT_DMD</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -8092,12 +8092,12 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>C_OFFC-SH</t>
+          <t>AHORT-Trac-MoTP-Mob</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>GDP</t>
+          <t>AGR_AHORT_DMD</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -8119,12 +8119,12 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>C_OFFC-WH</t>
+          <t>AHORT-Uti-MoTP-Mob</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>GDP</t>
+          <t>AGR_AHORT_DMD</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>C_OTH-LT</t>
+          <t>AINDC-Boiler-SH</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Constant</t>
+          <t>AGR_AINDC_DMD</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -8173,12 +8173,12 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>C_OTH-MPM</t>
+          <t>AINDC-LT</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Constant</t>
+          <t>AGR_AINDC_DMD</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -8200,12 +8200,12 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>C_OTH-MPS</t>
+          <t>AINDC-MoTP-Stat</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Constant</t>
+          <t>AGR_AINDC_DMD</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -8227,12 +8227,12 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>C_OTH-OTH</t>
+          <t>ALIVE-Bike-MoTP-Mob</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Constant</t>
+          <t>AGR_ALIVE_DMD</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>C_OTH-PH</t>
+          <t>ALIVE-IRG</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Constant</t>
+          <t>AGR_ALIVE_DMD</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -8281,12 +8281,12 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>C_OTH-PUMP</t>
+          <t>ALIVE-LT</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Constant</t>
+          <t>AGR_ALIVE_DMD</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -8308,12 +8308,12 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>C_OTH-SC</t>
+          <t>ALIVE-MTr-MoTP-Mob</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Constant</t>
+          <t>AGR_ALIVE_DMD</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -8335,12 +8335,12 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>C_OTH-SH</t>
+          <t>ALIVE-Trac-MoTP-Mob</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Constant</t>
+          <t>AGR_ALIVE_DMD</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -8362,12 +8362,12 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>C_OTH-WH</t>
+          <t>ALIVE-Uti-MoTP-Mob</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Constant</t>
+          <t>AGR_ALIVE_DMD</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -8389,12 +8389,12 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>C_WSR-CK</t>
+          <t>ALUM-EFURNC-PH_HIGH</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>GDP</t>
+          <t>IND_ALUM_DMD</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -8416,12 +8416,12 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>C_WSR-LT</t>
+          <t>AOTH-Furnace-PH</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>GDP</t>
+          <t>AGR_AOTH_DMD</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>C_WSR-MPM</t>
+          <t>AOTH-MoTP-Stat</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>GDP</t>
+          <t>AGR_AOTH_DMD</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -8470,12 +8470,12 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>C_WSR-MPS</t>
+          <t>AOTH-PH</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>GDP</t>
+          <t>AGR_AOTH_DMD</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -8497,12 +8497,12 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>C_WSR-OTH</t>
+          <t>AOTH-SH</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>GDP</t>
+          <t>AGR_AOTH_DMD</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -8524,12 +8524,12 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>C_WSR-RF</t>
+          <t>CNST-ELCTR-ELCTR</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>GDP</t>
+          <t>IND_CNST_DMD</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>C_WSR-SC</t>
+          <t>CNST-ENGIN-MTV_STA</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>GDP</t>
+          <t>IND_CNST_DMD</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -8578,12 +8578,12 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>C_WSR-SH</t>
+          <t>CNST-ICENG-MTV_MOB</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>GDP</t>
+          <t>IND_CNST_DMD</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -8605,12 +8605,12 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>C_WSR-WH</t>
+          <t>CNST-LIGHT-LIGHT</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>GDP</t>
+          <t>IND_CNST_DMD</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -8632,12 +8632,12 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>DARY-ACOMP-COMP_AIR</t>
+          <t>CNST-MOTOR-MTV_STA</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>IND_DARY_DMD</t>
+          <t>IND_CNST_DMD</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>DARY-BOILR-PH_INT</t>
+          <t>CNST-SH_LOW</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>IND_DARY_DMD</t>
+          <t>IND_CNST_DMD</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -8686,12 +8686,12 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>DARY-BOILR-PH_LOW</t>
+          <t>C_DATA-LT</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>IND_DARY_DMD</t>
+          <t>COM_DATA_DMD</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -8713,12 +8713,12 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>DARY-BOILR-WH_LOW</t>
+          <t>C_DATA-OTH</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>IND_DARY_DMD</t>
+          <t>COM_DATA_DMD</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>DARY-FAN-FAN</t>
+          <t>C_DATA-SC</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>IND_DARY_DMD</t>
+          <t>COM_DATA_DMD</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -8767,12 +8767,12 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>DARY-FRIDG-FRIDG</t>
+          <t>C_EDU-Boiler-SH</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>IND_DARY_DMD</t>
+          <t>POP</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -8794,12 +8794,12 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>DARY-LIGHT-LIGHT</t>
+          <t>C_EDU-Boiler-WH</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>IND_DARY_DMD</t>
+          <t>POP</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>DARY-MOTOR-MTV_STA</t>
+          <t>C_EDU-LT</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>IND_DARY_DMD</t>
+          <t>POP</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -8848,12 +8848,12 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>DARY-PUMP-PUMP</t>
+          <t>C_EDU-MPM</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>IND_DARY_DMD</t>
+          <t>POP</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -8875,12 +8875,12 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>DARY-SH_LOW</t>
+          <t>C_EDU-MPS</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>IND_DARY_DMD</t>
+          <t>POP</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -8902,7 +8902,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>DD-CH_INT</t>
+          <t>C_EDU-OTH</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -8929,7 +8929,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>DD-C_DRY</t>
+          <t>C_EDU-RF</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -8956,7 +8956,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>DD-C_WASH</t>
+          <t>C_EDU-RH-SH</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -8983,7 +8983,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>DD-D_WASH</t>
+          <t>C_EDU-SC</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -9010,7 +9010,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>DD-ELCTR</t>
+          <t>C_EDU-SH</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -9037,7 +9037,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>DD-FRIDG</t>
+          <t>C_EDU-WH</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -9064,7 +9064,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>DD-LIGHT</t>
+          <t>C_HLTH-Boiler-PH</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -9091,7 +9091,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>DD-MTV_MOB</t>
+          <t>C_HLTH-Boiler-SH</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -9118,7 +9118,7 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>DD-S_COOL</t>
+          <t>C_HLTH-Boiler-WH</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -9145,7 +9145,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>DD-S_HEAT</t>
+          <t>C_HLTH-Burner-PH</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -9172,7 +9172,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>DD-WH_LOW</t>
+          <t>C_HLTH-LT</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -9199,12 +9199,12 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>FOOD-ACOMP-COMP_AIR</t>
+          <t>C_HLTH-MPM</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>IND_FOOD_DMD</t>
+          <t>POP</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -9226,12 +9226,12 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>FOOD-BOILR-PH_INT</t>
+          <t>C_HLTH-MPS</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>IND_FOOD_DMD</t>
+          <t>POP</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -9253,12 +9253,12 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>FOOD-BOILR-PH_LOW</t>
+          <t>C_HLTH-OTH</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>IND_FOOD_DMD</t>
+          <t>POP</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
@@ -9280,12 +9280,12 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>FOOD-BOILR-WH_LOW</t>
+          <t>C_HLTH-RF</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>IND_FOOD_DMD</t>
+          <t>POP</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -9307,12 +9307,12 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>FOOD-ELCTR-ELCTR</t>
+          <t>C_HLTH-RH-PH</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>IND_FOOD_DMD</t>
+          <t>POP</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
@@ -9334,12 +9334,12 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>FOOD-FRIDG-FRIDG</t>
+          <t>C_HLTH-RH-SH</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>IND_FOOD_DMD</t>
+          <t>POP</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
@@ -9361,12 +9361,12 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>FOOD-IOVEN-CH_INT</t>
+          <t>C_HLTH-SC</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>IND_FOOD_DMD</t>
+          <t>POP</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -9388,12 +9388,12 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>FOOD-LIGHT-LIGHT</t>
+          <t>C_HLTH-SH</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>IND_FOOD_DMD</t>
+          <t>POP</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>FOOD-MOTOR-MTV_STA</t>
+          <t>C_HLTH-WH</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>IND_FOOD_DMD</t>
+          <t>POP</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -9442,12 +9442,12 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>FOOD-PUMP-PUMP</t>
+          <t>C_OFFC-Boiler-SH</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>IND_FOOD_DMD</t>
+          <t>GDP</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -9469,12 +9469,12 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>FOOD-SH_LOW</t>
+          <t>C_OFFC-Boiler-WH</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>IND_FOOD_DMD</t>
+          <t>GDP</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
@@ -9496,12 +9496,12 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>JD-CH_INT</t>
+          <t>C_OFFC-LT</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>POP</t>
+          <t>GDP</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
@@ -9523,12 +9523,12 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>JD-C_DRY</t>
+          <t>C_OFFC-MPM</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>POP</t>
+          <t>GDP</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
@@ -9550,12 +9550,12 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>JD-C_WASH</t>
+          <t>C_OFFC-MPS</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>POP</t>
+          <t>GDP</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
@@ -9577,12 +9577,12 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>JD-D_WASH</t>
+          <t>C_OFFC-OTH</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>POP</t>
+          <t>GDP</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
@@ -9604,12 +9604,12 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>JD-ELCTR</t>
+          <t>C_OFFC-RH-SH</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>POP</t>
+          <t>GDP</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
@@ -9631,12 +9631,12 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>JD-FRIDG</t>
+          <t>C_OFFC-SC</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>POP</t>
+          <t>GDP</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
@@ -9658,12 +9658,12 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>JD-LIGHT</t>
+          <t>C_OFFC-SH</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>POP</t>
+          <t>GDP</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>JD-MTV_MOB</t>
+          <t>C_OFFC-WH</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>POP</t>
+          <t>GDP</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
@@ -9712,12 +9712,12 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>JD-S_COOL</t>
+          <t>C_OTH-Boiler-SH</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>POP</t>
+          <t>Constant</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
@@ -9739,12 +9739,12 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>JD-S_HEAT</t>
+          <t>C_OTH-Boiler-WH</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>POP</t>
+          <t>Constant</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
@@ -9766,12 +9766,12 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>JD-WH_LOW</t>
+          <t>C_OTH-Burner-PH</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>POP</t>
+          <t>Constant</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
@@ -9793,12 +9793,12 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>MEAT-BOILR-PH_INT</t>
+          <t>C_OTH-LT</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>IND_MEAT_DMD</t>
+          <t>Constant</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
@@ -9820,12 +9820,12 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>MEAT-BOILR-WH_LOW</t>
+          <t>C_OTH-MPM</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>IND_MEAT_DMD</t>
+          <t>Constant</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>MEAT-FRIDG-FRIDG</t>
+          <t>C_OTH-MPS</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>IND_MEAT_DMD</t>
+          <t>Constant</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
@@ -9874,12 +9874,12 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>MEAT-HEATR-WH_LOW</t>
+          <t>C_OTH-OTH</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>IND_MEAT_DMD</t>
+          <t>Constant</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
@@ -9901,12 +9901,12 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>MEAT-LIGHT-LIGHT</t>
+          <t>C_OTH-PUMP</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>IND_MEAT_DMD</t>
+          <t>Constant</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>MEAT-MOTOR-MTV_STA</t>
+          <t>C_OTH-RH-SH</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>IND_MEAT_DMD</t>
+          <t>Constant</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
@@ -9955,12 +9955,12 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>MINE-BOILR-PH_INT</t>
+          <t>C_OTH-SC</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>IND_MINE_DMD</t>
+          <t>Constant</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
@@ -9982,12 +9982,12 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>MINE-ELCTR-ELCTR</t>
+          <t>C_OTH-SH</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>IND_MINE_DMD</t>
+          <t>Constant</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
@@ -10009,12 +10009,12 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>MINE-ENGIN-MTV_STA</t>
+          <t>C_OTH-WH</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>IND_MINE_DMD</t>
+          <t>Constant</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
@@ -10036,12 +10036,12 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>MINE-ICENG-MTV_MOB</t>
+          <t>C_WSR-Boiler-SH</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>IND_MINE_DMD</t>
+          <t>GDP</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>MINE-LIGHT-LIGHT</t>
+          <t>C_WSR-Boiler-WH</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>IND_MINE_DMD</t>
+          <t>GDP</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
@@ -10090,12 +10090,12 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>MINE-MOTOR-MTV_STA</t>
+          <t>C_WSR-Burner-SH</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>IND_MINE_DMD</t>
+          <t>GDP</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
@@ -10117,12 +10117,12 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>MINE-SH_LOW</t>
+          <t>C_WSR-CK</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>IND_MINE_DMD</t>
+          <t>GDP</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
@@ -10144,12 +10144,12 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>MNRL-FURNC-PH_HIGH</t>
+          <t>C_WSR-LT</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>IND_MNRL_DMD</t>
+          <t>GDP</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
@@ -10171,12 +10171,12 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>MNRL-LIGHT-LIGHT</t>
+          <t>C_WSR-MPM</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>IND_MNRL_DMD</t>
+          <t>GDP</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
@@ -10198,12 +10198,12 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>MNRL-MOTOR-MTV_STA</t>
+          <t>C_WSR-MPS</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>IND_MNRL_DMD</t>
+          <t>GDP</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>MNRL-PUMP-PUMP</t>
+          <t>C_WSR-OTH</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>IND_MNRL_DMD</t>
+          <t>GDP</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
@@ -10252,12 +10252,12 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>OTHR-BOILR-PH_INT</t>
+          <t>C_WSR-RF</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Constant</t>
+          <t>GDP</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
@@ -10279,12 +10279,12 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>OTHR-BOILR-PH_LOW</t>
+          <t>C_WSR-RH-SH</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Constant</t>
+          <t>GDP</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>OTHR-EFURNC-PH_HIGH</t>
+          <t>C_WSR-SC</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Constant</t>
+          <t>GDP</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
@@ -10333,12 +10333,12 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>OTHR-ELCTR-ELCTR</t>
+          <t>C_WSR-SH</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Constant</t>
+          <t>GDP</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
@@ -10360,12 +10360,12 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>OTHR-FURNC-PH_HIGH</t>
+          <t>C_WSR-WH</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Constant</t>
+          <t>GDP</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
@@ -10387,12 +10387,12 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>OTHR-HEATR-PH_INT</t>
+          <t>DARY-ACOMP-COMP_AIR</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Constant</t>
+          <t>IND_DARY_DMD</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
@@ -10414,12 +10414,12 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>OTHR-HEATR-PH_LOW</t>
+          <t>DARY-BOILR-PH_INT</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Constant</t>
+          <t>IND_DARY_DMD</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>OTHR-ICENG-MTV_MOB</t>
+          <t>DARY-BOILR-PH_LOW</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Constant</t>
+          <t>IND_DARY_DMD</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
@@ -10468,12 +10468,12 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>OTHR-LIGHT-LIGHT</t>
+          <t>DARY-BOILR-WH_LOW</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Constant</t>
+          <t>IND_DARY_DMD</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
@@ -10495,12 +10495,12 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>OTHR-MOTOR-MTV_STA</t>
+          <t>DARY-FAN-FAN</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Constant</t>
+          <t>IND_DARY_DMD</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
@@ -10522,12 +10522,12 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>OTHR-PUMP-PUMP</t>
+          <t>DARY-FRIDG-FRIDG</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Constant</t>
+          <t>IND_DARY_DMD</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
@@ -10549,12 +10549,12 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>T_C_Car</t>
+          <t>DARY-LIGHT-LIGHT</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>TRA_LCV_DEM</t>
+          <t>IND_DARY_DMD</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>T_F_DSHIP</t>
+          <t>DARY-MOTOR-MTV_STA</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>GDP</t>
+          <t>IND_DARY_DMD</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
@@ -10603,12 +10603,12 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>T_F_HTrk</t>
+          <t>DARY-PUMP-PUMP</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>TRA_HTRK_DEM</t>
+          <t>IND_DARY_DMD</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
@@ -10630,12 +10630,12 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>T_F_ISHIP</t>
+          <t>DARY-SH_LOW</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>GDP</t>
+          <t>IND_DARY_DMD</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
@@ -10657,12 +10657,12 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>T_F_LTrk</t>
+          <t>DD-CH_INT</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>TRA_LTRK_DEM</t>
+          <t>POP</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
@@ -10684,12 +10684,12 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>T_F_MTrk</t>
+          <t>DD-C_DRY</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>TRA_MTRK_DEM</t>
+          <t>POP</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>T_F_Rail</t>
+          <t>DD-C_WASH</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>GDP</t>
+          <t>POP</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>T_O_JET</t>
+          <t>DD-D_WASH</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
@@ -10765,7 +10765,7 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>T_O_JET_Int</t>
+          <t>DD-ELCTR</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -10792,12 +10792,12 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>T_P_Bus</t>
+          <t>DD-FRIDG</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>TRA_BUS_DEM</t>
+          <t>POP</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
@@ -10819,12 +10819,12 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>T_P_Car</t>
+          <t>DD-LIGHT</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>TRA_LPV_DEM</t>
+          <t>POP</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
@@ -10846,12 +10846,12 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>T_P_Mcy</t>
+          <t>DD-MTV_MOB</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>TRA_MCY_DEM</t>
+          <t>POP</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
@@ -10873,12 +10873,12 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>T_P_Rail</t>
+          <t>DD-S_COOL</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>GDP</t>
+          <t>POP</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>WOOD-ACOMP-COMP_AIR</t>
+          <t>DD-S_HEAT</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>IND_WOOD_DMD</t>
+          <t>POP</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>WOOD-BOILR-PH_INT</t>
+          <t>DD-WH_LOW</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>IND_WOOD_DMD</t>
+          <t>POP</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
@@ -10954,12 +10954,12 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>WOOD-BURNR-PH_INT</t>
+          <t>FOOD-ACOMP-COMP_AIR</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>IND_WOOD_DMD</t>
+          <t>IND_FOOD_DMD</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
@@ -10981,12 +10981,12 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>WOOD-ELCTR-ELCTR</t>
+          <t>FOOD-BOILR-PH_INT</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>IND_WOOD_DMD</t>
+          <t>IND_FOOD_DMD</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
@@ -11008,12 +11008,12 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>WOOD-FAN-FAN</t>
+          <t>FOOD-BOILR-PH_LOW</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>IND_WOOD_DMD</t>
+          <t>IND_FOOD_DMD</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>WOOD-HPPH-PH_LOW</t>
+          <t>FOOD-BOILR-WH_LOW</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>IND_WOOD_DMD</t>
+          <t>IND_FOOD_DMD</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
@@ -11062,12 +11062,12 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>WOOD-LIGHT-LIGHT</t>
+          <t>FOOD-ELCTR-ELCTR</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>IND_WOOD_DMD</t>
+          <t>IND_FOOD_DMD</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
@@ -11089,12 +11089,12 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>WOOD-MOTOR-MTV_STA</t>
+          <t>FOOD-FRIDG-FRIDG</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>IND_WOOD_DMD</t>
+          <t>IND_FOOD_DMD</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
@@ -11116,12 +11116,12 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>WOOD-PUMP-PUMP</t>
+          <t>FOOD-IOVEN-CH_INT</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>IND_WOOD_DMD</t>
+          <t>IND_FOOD_DMD</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
@@ -11143,20 +11143,1775 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
+          <t>FOOD-LIGHT-LIGHT</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>IND_FOOD_DMD</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>FOOD-MOTOR-MTV_STA</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>IND_FOOD_DMD</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>FOOD-PUMP-PUMP</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>IND_FOOD_DMD</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>FOOD-SH_LOW</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>IND_FOOD_DMD</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>JD-CH_INT</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>POP</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>JD-C_DRY</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>POP</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>JD-C_WASH</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>POP</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>JD-D_WASH</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>POP</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>JD-ELCTR</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>POP</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>JD-FRIDG</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>POP</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>JD-LIGHT</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>POP</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>JD-MTV_MOB</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>POP</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>JD-S_COOL</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>POP</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>JD-S_HEAT</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>POP</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>JD-WH_LOW</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>POP</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>MEAT-BOILR-PH_INT</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>IND_MEAT_DMD</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>MEAT-BOILR-WH_LOW</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>IND_MEAT_DMD</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>MEAT-FRIDG-FRIDG</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>IND_MEAT_DMD</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>MEAT-HEATR-WH_LOW</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>IND_MEAT_DMD</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>MEAT-LIGHT-LIGHT</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>IND_MEAT_DMD</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>MEAT-MOTOR-MTV_STA</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>IND_MEAT_DMD</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>MINE-BOILR-PH_INT</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>IND_MINE_DMD</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>MINE-ELCTR-ELCTR</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>IND_MINE_DMD</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>MINE-ENGIN-MTV_STA</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>IND_MINE_DMD</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>MINE-ICENG-MTV_MOB</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>IND_MINE_DMD</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>MINE-LIGHT-LIGHT</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>IND_MINE_DMD</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>MINE-MOTOR-MTV_STA</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>IND_MINE_DMD</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>MINE-SH_LOW</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>IND_MINE_DMD</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>MNRL-FURNC-PH_HIGH</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>IND_MNRL_DMD</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>MNRL-LIGHT-LIGHT</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>IND_MNRL_DMD</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>MNRL-MOTOR-MTV_STA</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>IND_MNRL_DMD</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>MNRL-PUMP-PUMP</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>IND_MNRL_DMD</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>OTHR-BOILR-PH_INT</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>OTHR-BOILR-PH_LOW</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>OTHR-EFURNC-PH_HIGH</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>OTHR-ELCTR-ELCTR</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>OTHR-FURNC-PH_HIGH</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>OTHR-HEATR-PH_INT</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>OTHR-HEATR-PH_LOW</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>OTHR-ICENG-MTV_MOB</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>OTHR-LIGHT-LIGHT</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>OTHR-MOTOR-MTV_STA</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>OTHR-PUMP-PUMP</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>T_C_Car</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>TRA_LCV_DEM</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>T_F_DSHIP</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>GDP</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>T_F_HTrk</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>TRA_HTRK_DEM</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>T_F_ISHIP</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>GDP</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>T_F_LTrk</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>TRA_LTRK_DEM</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>T_F_MTrk</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>TRA_MTRK_DEM</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>T_F_Rail</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>GDP</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>T_O_JET</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>POP</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>T_O_JET_Int</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>POP</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>T_P_Bus</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>TRA_BUS_DEM</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>T_P_Car</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>TRA_LPV_DEM</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>T_P_Mcy</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>TRA_MCY_DEM</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>T_P_Rail</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>GDP</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>WOOD-ACOMP-COMP_AIR</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>IND_WOOD_DMD</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>WOOD-BOILR-PH_INT</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>IND_WOOD_DMD</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>WOOD-BURNR-PH_INT</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>IND_WOOD_DMD</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>WOOD-ELCTR-ELCTR</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>IND_WOOD_DMD</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>WOOD-FAN-FAN</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>IND_WOOD_DMD</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>WOOD-HPPH-PH_LOW</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>IND_WOOD_DMD</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>WOOD-LIGHT-LIGHT</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>IND_WOOD_DMD</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>WOOD-MOTOR-MTV_STA</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>IND_WOOD_DMD</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>WOOD-PUMP-PUMP</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>IND_WOOD_DMD</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
           <t>WOOD-REFIN-REFIN</t>
         </is>
       </c>
-      <c r="C399" t="inlineStr">
+      <c r="C464" t="inlineStr">
         <is>
           <t>IND_WOOD_DMD</t>
         </is>
       </c>
-      <c r="D399" t="inlineStr">
-        <is>
-          <t>Constant</t>
-        </is>
-      </c>
-      <c r="E399" t="inlineStr">
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr">
         <is>
           <t>Constant</t>
         </is>
